--- a/Data/testDataRomania - Copy (8).xlsx
+++ b/Data/testDataRomania - Copy (8).xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E740F471-AF0E-474A-8456-1AC7E72F71E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF9D883-A929-42A5-87D1-433EAB3B64C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="620" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1420,8 +1419,8 @@
         <v>81</v>
       </c>
       <c r="K2" s="13" t="str">
-        <f t="shared" ref="K2:K17" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/07/2024</v>
+        <f t="shared" ref="K2:K16" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>02/10/2024</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>79</v>
@@ -1457,8 +1456,8 @@
         <v>81</v>
       </c>
       <c r="W2" s="13" t="str">
-        <f t="shared" ref="W2:W17" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/07/2024</v>
+        <f t="shared" ref="W2:W16" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>02/10/2024</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>88</v>
@@ -1528,7 +1527,7 @@
       </c>
       <c r="AT2" s="19" t="str">
         <f t="shared" ref="AT2:AT16" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU2" s="10" t="s">
         <v>105</v>
@@ -1544,14 +1543,14 @@
       </c>
       <c r="AY2" s="13" t="str">
         <f t="shared" ref="AY2:AZ16" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ2" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA2" s="44" t="str">
-        <f>AH2</f>
+        <f t="shared" ref="BA2:BA16" si="4">AH2</f>
         <v>N/A</v>
       </c>
       <c r="BB2" s="21" t="s">
@@ -1667,7 +1666,7 @@
       </c>
       <c r="K3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L3" s="17" t="s">
         <v>79</v>
@@ -1704,7 +1703,7 @@
       </c>
       <c r="W3" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X3" s="12" t="s">
         <v>88</v>
@@ -1738,7 +1737,7 @@
       </c>
       <c r="AH3" s="44">
         <f ca="1">W3+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI3" s="12" t="s">
         <v>96</v>
@@ -1775,7 +1774,7 @@
       </c>
       <c r="AT3" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU3" s="10" t="s">
         <v>105</v>
@@ -1791,15 +1790,15 @@
       </c>
       <c r="AY3" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ3" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA3" s="44">
-        <f ca="1">AH3</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB3" s="21" t="s">
         <v>79</v>
@@ -1914,7 +1913,7 @@
       </c>
       <c r="K4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>79</v>
@@ -1951,7 +1950,7 @@
       </c>
       <c r="W4" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X4" s="12" t="s">
         <v>88</v>
@@ -1985,7 +1984,7 @@
       </c>
       <c r="AH4" s="44">
         <f ca="1">W4+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI4" s="12" t="s">
         <v>96</v>
@@ -2022,7 +2021,7 @@
       </c>
       <c r="AT4" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU4" s="10" t="s">
         <v>105</v>
@@ -2038,15 +2037,15 @@
       </c>
       <c r="AY4" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ4" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA4" s="44">
-        <f ca="1">AH4</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB4" s="21" t="s">
         <v>79</v>
@@ -2161,7 +2160,7 @@
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>79</v>
@@ -2198,7 +2197,7 @@
       </c>
       <c r="W5" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X5" s="12" t="s">
         <v>88</v>
@@ -2232,7 +2231,7 @@
       </c>
       <c r="AH5" s="44">
         <f ca="1">W5+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI5" s="12" t="s">
         <v>96</v>
@@ -2269,7 +2268,7 @@
       </c>
       <c r="AT5" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU5" s="10" t="s">
         <v>105</v>
@@ -2285,15 +2284,15 @@
       </c>
       <c r="AY5" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ5" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA5" s="44">
-        <f ca="1">AH5</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB5" s="21" t="s">
         <v>79</v>
@@ -2408,7 +2407,7 @@
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>79</v>
@@ -2445,7 +2444,7 @@
       </c>
       <c r="W6" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X6" s="12" t="s">
         <v>88</v>
@@ -2515,7 +2514,7 @@
       </c>
       <c r="AT6" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU6" s="10" t="s">
         <v>105</v>
@@ -2531,14 +2530,14 @@
       </c>
       <c r="AY6" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ6" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA6" s="44" t="str">
-        <f>AH6</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB6" s="21" t="s">
@@ -2654,7 +2653,7 @@
       </c>
       <c r="K7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L7" s="17" t="s">
         <v>79</v>
@@ -2691,7 +2690,7 @@
       </c>
       <c r="W7" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X7" s="12" t="s">
         <v>88</v>
@@ -2725,7 +2724,7 @@
       </c>
       <c r="AH7" s="44">
         <f ca="1">W7+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI7" s="12" t="s">
         <v>96</v>
@@ -2762,7 +2761,7 @@
       </c>
       <c r="AT7" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU7" s="10" t="s">
         <v>105</v>
@@ -2778,15 +2777,15 @@
       </c>
       <c r="AY7" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ7" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA7" s="44">
-        <f ca="1">AH7</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB7" s="21" t="s">
         <v>79</v>
@@ -2901,7 +2900,7 @@
       </c>
       <c r="K8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>79</v>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="W8" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X8" s="12" t="s">
         <v>88</v>
@@ -3008,7 +3007,7 @@
       </c>
       <c r="AT8" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU8" s="10" t="s">
         <v>105</v>
@@ -3024,14 +3023,14 @@
       </c>
       <c r="AY8" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ8" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA8" s="44" t="str">
-        <f>AH8</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB8" s="21" t="s">
@@ -3147,7 +3146,7 @@
       </c>
       <c r="K9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L9" s="17" t="s">
         <v>79</v>
@@ -3184,7 +3183,7 @@
       </c>
       <c r="W9" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X9" s="12" t="s">
         <v>88</v>
@@ -3218,7 +3217,7 @@
       </c>
       <c r="AH9" s="44">
         <f ca="1">W9+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI9" s="12" t="s">
         <v>96</v>
@@ -3255,7 +3254,7 @@
       </c>
       <c r="AT9" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU9" s="10" t="s">
         <v>105</v>
@@ -3271,15 +3270,15 @@
       </c>
       <c r="AY9" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ9" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA9" s="44">
-        <f ca="1">AH9</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB9" s="21" t="s">
         <v>79</v>
@@ -3393,7 +3392,7 @@
       </c>
       <c r="K10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>79</v>
@@ -3430,7 +3429,7 @@
       </c>
       <c r="W10" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X10" s="12" t="s">
         <v>88</v>
@@ -3500,7 +3499,7 @@
       </c>
       <c r="AT10" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU10" s="10" t="s">
         <v>105</v>
@@ -3516,14 +3515,14 @@
       </c>
       <c r="AY10" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ10" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA10" s="44" t="str">
-        <f>AH10</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB10" s="21" t="s">
@@ -3638,7 +3637,7 @@
       </c>
       <c r="K11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L11" s="17" t="s">
         <v>79</v>
@@ -3675,7 +3674,7 @@
       </c>
       <c r="W11" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X11" s="12" t="s">
         <v>88</v>
@@ -3709,7 +3708,7 @@
       </c>
       <c r="AH11" s="44">
         <f ca="1">W11+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI11" s="12" t="s">
         <v>96</v>
@@ -3746,7 +3745,7 @@
       </c>
       <c r="AT11" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU11" s="10" t="s">
         <v>105</v>
@@ -3762,15 +3761,15 @@
       </c>
       <c r="AY11" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ11" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA11" s="44">
-        <f ca="1">AH11</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB11" s="21" t="s">
         <v>79</v>
@@ -3884,7 +3883,7 @@
       </c>
       <c r="K12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>79</v>
@@ -3921,7 +3920,7 @@
       </c>
       <c r="W12" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>88</v>
@@ -3991,7 +3990,7 @@
       </c>
       <c r="AT12" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU12" s="10" t="s">
         <v>105</v>
@@ -4007,14 +4006,14 @@
       </c>
       <c r="AY12" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ12" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA12" s="44" t="str">
-        <f>AH12</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB12" s="21" t="s">
@@ -4129,7 +4128,7 @@
       </c>
       <c r="K13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L13" s="17" t="s">
         <v>79</v>
@@ -4166,7 +4165,7 @@
       </c>
       <c r="W13" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X13" s="12" t="s">
         <v>88</v>
@@ -4200,7 +4199,7 @@
       </c>
       <c r="AH13" s="44">
         <f ca="1">W13+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI13" s="12" t="s">
         <v>96</v>
@@ -4237,7 +4236,7 @@
       </c>
       <c r="AT13" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU13" s="10" t="s">
         <v>105</v>
@@ -4253,15 +4252,15 @@
       </c>
       <c r="AY13" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ13" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA13" s="44">
-        <f ca="1">AH13</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB13" s="21" t="s">
         <v>79</v>
@@ -4374,7 +4373,7 @@
       </c>
       <c r="K14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>79</v>
@@ -4411,7 +4410,7 @@
       </c>
       <c r="W14" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X14" s="12" t="s">
         <v>88</v>
@@ -4481,7 +4480,7 @@
       </c>
       <c r="AT14" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU14" s="10" t="s">
         <v>105</v>
@@ -4497,14 +4496,14 @@
       </c>
       <c r="AY14" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ14" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA14" s="44" t="str">
-        <f>AH14</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB14" s="21" t="s">
@@ -4618,7 +4617,7 @@
       </c>
       <c r="K15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L15" s="17" t="s">
         <v>79</v>
@@ -4655,7 +4654,7 @@
       </c>
       <c r="W15" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X15" s="12" t="s">
         <v>88</v>
@@ -4725,7 +4724,7 @@
       </c>
       <c r="AT15" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU15" s="10" t="s">
         <v>105</v>
@@ -4741,14 +4740,14 @@
       </c>
       <c r="AY15" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ15" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA15" s="44" t="str">
-        <f>AH15</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="BB15" s="21" t="s">
@@ -4862,7 +4861,7 @@
       </c>
       <c r="K16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>79</v>
@@ -4899,7 +4898,7 @@
       </c>
       <c r="W16" s="13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="X16" s="12" t="s">
         <v>88</v>
@@ -4933,7 +4932,7 @@
       </c>
       <c r="AH16" s="44">
         <f ca="1">W16+360</f>
-        <v>45836</v>
+        <v>45927</v>
       </c>
       <c r="AI16" s="12" t="s">
         <v>96</v>
@@ -4970,7 +4969,7 @@
       </c>
       <c r="AT16" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AU16" s="10" t="s">
         <v>105</v>
@@ -4986,15 +4985,15 @@
       </c>
       <c r="AY16" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="AZ16" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>03/07/2024</v>
+        <v>02/10/2024</v>
       </c>
       <c r="BA16" s="44">
-        <f ca="1">AH16</f>
-        <v>45836</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45927</v>
       </c>
       <c r="BB16" s="21" t="s">
         <v>79</v>
